--- a/data/data_monitoreo_cruceta.xlsx
+++ b/data/data_monitoreo_cruceta.xlsx
@@ -443,101 +443,101 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MAZA RIOFRIO CINTHIA NATELAHI</t>
+          <t>PANTA VARONA CANDY ELIZABETH</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>129</v>
+        <v>212</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>VEGA ZAPATA JESUS GABRIEL</t>
+          <t>ELIAS MACHADO JUANA MARGOT</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>125</v>
+        <v>210</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PANTA VARONA CANDY ELIZABETH</t>
+          <t>MAZA RIOFRIO CINTHIA NATELAHI</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>123</v>
+        <v>208</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PALACIOS PANTA LUIS MIGUEL</t>
+          <t>CRISANTO CARMEN ROSITA ABIGAIL</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>123</v>
+        <v>198</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PANTA NIMA FREDDY ROLAND JUNIOR</t>
+          <t>PALACIOS PANTA LUIS MIGUEL</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>123</v>
+        <v>197</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CRISANTO CARMEN ROSITA ABIGAIL</t>
+          <t>HIDALGO MOSCOL YESSICA JAZMIN</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>119</v>
+        <v>196</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ELIAS MACHADO JUANA MARGOT</t>
+          <t>PANTA NIMA FREDDY ROLAND JUNIOR</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>119</v>
+        <v>194</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SALAZAR VEGA MARIA FERNANDA</t>
+          <t>VEGA ZAPATA JESUS GABRIEL</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>119</v>
+        <v>191</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HIDALGO MOSCOL YESSICA JAZMIN</t>
+          <t>TALLEDO ELIAS ANDREA ALESSANDRA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>112</v>
+        <v>189</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TALLEDO ELIAS ANDREA ALESSANDRA</t>
+          <t>SALAZAR VEGA MARIA FERNANDA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>107</v>
+        <v>181</v>
       </c>
     </row>
   </sheetData>

--- a/data/data_monitoreo_cruceta.xlsx
+++ b/data/data_monitoreo_cruceta.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>212</v>
+        <v>227</v>
       </c>
     </row>
     <row r="3">
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>210</v>
+        <v>220</v>
       </c>
     </row>
     <row r="4">
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>208</v>
+        <v>220</v>
       </c>
     </row>
     <row r="5">
@@ -477,27 +477,27 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>198</v>
+        <v>211</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PALACIOS PANTA LUIS MIGUEL</t>
+          <t>HIDALGO MOSCOL YESSICA JAZMIN</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>197</v>
+        <v>209</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HIDALGO MOSCOL YESSICA JAZMIN</t>
+          <t>PALACIOS PANTA LUIS MIGUEL</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>196</v>
+        <v>208</v>
       </c>
     </row>
     <row r="8">
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>194</v>
+        <v>206</v>
       </c>
     </row>
     <row r="9">
@@ -517,27 +517,27 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>191</v>
+        <v>206</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TALLEDO ELIAS ANDREA ALESSANDRA</t>
+          <t>SALAZAR VEGA MARIA FERNANDA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>189</v>
+        <v>201</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SALAZAR VEGA MARIA FERNANDA</t>
+          <t>TALLEDO ELIAS ANDREA ALESSANDRA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>181</v>
+        <v>196</v>
       </c>
     </row>
   </sheetData>

--- a/data/data_monitoreo_cruceta.xlsx
+++ b/data/data_monitoreo_cruceta.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>227</v>
+        <v>241</v>
       </c>
     </row>
     <row r="3">
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>220</v>
+        <v>232</v>
       </c>
     </row>
     <row r="4">
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>220</v>
+        <v>232</v>
       </c>
     </row>
     <row r="5">
@@ -477,7 +477,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>211</v>
+        <v>224</v>
       </c>
     </row>
     <row r="6">
@@ -487,37 +487,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>209</v>
+        <v>221</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PALACIOS PANTA LUIS MIGUEL</t>
+          <t>VEGA ZAPATA JESUS GABRIEL</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>208</v>
+        <v>220</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PANTA NIMA FREDDY ROLAND JUNIOR</t>
+          <t>PALACIOS PANTA LUIS MIGUEL</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>206</v>
+        <v>219</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>VEGA ZAPATA JESUS GABRIEL</t>
+          <t>PANTA NIMA FREDDY ROLAND JUNIOR</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>206</v>
+        <v>217</v>
       </c>
     </row>
     <row r="10">
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>201</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11">
@@ -537,7 +537,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>196</v>
+        <v>207</v>
       </c>
     </row>
   </sheetData>

--- a/data/data_monitoreo_cruceta.xlsx
+++ b/data/data_monitoreo_cruceta.xlsx
@@ -447,97 +447,97 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>241</v>
+        <v>274</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ELIAS MACHADO JUANA MARGOT</t>
+          <t>MAZA RIOFRIO CINTHIA NATELAHI</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>232</v>
+        <v>269</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MAZA RIOFRIO CINTHIA NATELAHI</t>
+          <t>PALACIOS PANTA LUIS MIGUEL</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>232</v>
+        <v>266</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CRISANTO CARMEN ROSITA ABIGAIL</t>
+          <t>ELIAS MACHADO JUANA MARGOT</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>224</v>
+        <v>263</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>HIDALGO MOSCOL YESSICA JAZMIN</t>
+          <t>CRISANTO CARMEN ROSITA ABIGAIL</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>221</v>
+        <v>262</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>VEGA ZAPATA JESUS GABRIEL</t>
+          <t>HIDALGO MOSCOL YESSICA JAZMIN</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>220</v>
+        <v>255</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PALACIOS PANTA LUIS MIGUEL</t>
+          <t>TALLEDO ELIAS ANDREA ALESSANDRA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>219</v>
+        <v>248</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>PANTA NIMA FREDDY ROLAND JUNIOR</t>
+          <t>SALAZAR VEGA MARIA FERNANDA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>217</v>
+        <v>248</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SALAZAR VEGA MARIA FERNANDA</t>
+          <t>VEGA ZAPATA JESUS GABRIEL</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>212</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TALLEDO ELIAS ANDREA ALESSANDRA</t>
+          <t>PANTA NIMA FREDDY ROLAND JUNIOR</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>207</v>
+        <v>243</v>
       </c>
     </row>
   </sheetData>

--- a/data/data_monitoreo_cruceta.xlsx
+++ b/data/data_monitoreo_cruceta.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>274</v>
+        <v>286</v>
       </c>
     </row>
     <row r="3">
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>269</v>
+        <v>275</v>
       </c>
     </row>
     <row r="4">
@@ -467,27 +467,27 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>266</v>
+        <v>272</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ELIAS MACHADO JUANA MARGOT</t>
+          <t>CRISANTO CARMEN ROSITA ABIGAIL</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>263</v>
+        <v>272</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CRISANTO CARMEN ROSITA ABIGAIL</t>
+          <t>ELIAS MACHADO JUANA MARGOT</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="7">
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>255</v>
+        <v>259</v>
       </c>
     </row>
     <row r="8">
@@ -507,37 +507,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>248</v>
+        <v>257</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SALAZAR VEGA MARIA FERNANDA</t>
+          <t>PANTA NIMA FREDDY ROLAND JUNIOR</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>248</v>
+        <v>253</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>VEGA ZAPATA JESUS GABRIEL</t>
+          <t>SALAZAR VEGA MARIA FERNANDA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>244</v>
+        <v>253</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>PANTA NIMA FREDDY ROLAND JUNIOR</t>
+          <t>VEGA ZAPATA JESUS GABRIEL</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>243</v>
+        <v>250</v>
       </c>
     </row>
   </sheetData>
